--- a/output/2026-09-08_19_Croazia_Sisacko-moslavacka_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-08_19_Croazia_Sisacko-moslavacka_Componentistica_Ventilazione_industriale.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
